--- a/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="11_13400C8A471826D5940B628CA6FCA9A8E4E8ED3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7899A3FB-9291-4FED-AA64-D74856A8A53B}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="11_13400C8A471826D5940B628CA6FCA9A8E4E8ED3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78F79966-FC3D-4E1D-A748-76A7B1698F4E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="124">
   <si>
     <t>Project ID</t>
   </si>
@@ -77,7 +77,7 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Comments</t>
+    <t>Tag</t>
   </si>
   <si>
     <t>SEH Taxonomy</t>
@@ -239,6 +239,9 @@
     <t>Funding Facility for Stabilization</t>
   </si>
   <si>
+    <t>https://open.undp.org/projects/00089459</t>
+  </si>
+  <si>
     <t>Nr of people with access to electricity</t>
   </si>
   <si>
@@ -282,6 +285,9 @@
   </si>
   <si>
     <t>MW</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
   <si>
     <t>1500 (50 % women)</t>
@@ -426,7 +432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +472,13 @@
       <color rgb="FFFF0000"/>
       <name val="Helvetica Neue"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -536,7 +549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -681,6 +694,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -689,7 +726,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -829,10 +866,166 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -853,32 +1046,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -937,18 +1115,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -961,61 +1127,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1323,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF5B37D-49A5-4ADB-B5FC-F6F25C4D7831}">
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -1336,87 +1448,85 @@
     <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" customWidth="1"/>
     <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="51.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="45.75">
-      <c r="A1" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="105" t="s">
+    <row r="1" spans="1:23" ht="45.75">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="105" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="105" t="s">
+      <c r="D1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="105" t="s">
+      <c r="F1" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105" t="s">
+      <c r="G1" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="105" t="s">
+      <c r="H1" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="107" t="s">
+      <c r="J1" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="107" t="s">
+      <c r="K1" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="107" t="s">
+      <c r="L1" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="107" t="s">
+      <c r="M1" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="107" t="s">
+      <c r="N1" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="107" t="s">
+      <c r="O1" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="107" t="s">
+      <c r="P1" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="107" t="s">
+      <c r="Q1" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="107" t="s">
+      <c r="R1" s="63" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-    </row>
-    <row r="2" spans="1:24" ht="60.75">
-      <c r="A2" s="35">
+    </row>
+    <row r="2" spans="1:23" ht="45.75">
+      <c r="A2" s="14">
         <v>122659</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="109">
+      <c r="D2" s="77">
         <v>149000</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="64" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -1434,36 +1544,35 @@
       <c r="J2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="111">
+      <c r="K2" s="65">
         <v>0.5</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>24</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="N2" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-    </row>
-    <row r="3" spans="1:24" ht="60.75">
-      <c r="A3" s="115">
+    </row>
+    <row r="3" spans="1:23" ht="45.75">
+      <c r="A3" s="80">
         <v>122627</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="122">
+      <c r="C3" s="83"/>
+      <c r="D3" s="82">
         <v>922000</v>
       </c>
-      <c r="E3" s="112" t="s">
+      <c r="E3" s="75" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -1475,34 +1584,33 @@
       <c r="H3" s="9">
         <v>1500</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="I3" s="72" t="s">
         <v>29</v>
       </c>
       <c r="J3" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="111">
+      <c r="K3" s="65">
         <v>0.5</v>
       </c>
-      <c r="L3" s="121"/>
+      <c r="L3" s="72"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="N3" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-    </row>
-    <row r="4" spans="1:24" ht="121.5">
-      <c r="A4" s="115"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="112" t="s">
+    </row>
+    <row r="4" spans="1:23" ht="121.5">
+      <c r="A4" s="85"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="75" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -1514,38 +1622,37 @@
       <c r="H4" s="9">
         <v>1000</v>
       </c>
-      <c r="I4" s="121"/>
+      <c r="I4" s="72"/>
       <c r="J4" s="35"/>
-      <c r="K4" s="111">
+      <c r="K4" s="65">
         <v>0.5</v>
       </c>
-      <c r="L4" s="121"/>
+      <c r="L4" s="72"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="N4" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-    </row>
-    <row r="5" spans="1:24" ht="90" customHeight="1">
-      <c r="A5" s="35">
+    </row>
+    <row r="5" spans="1:23" ht="90" customHeight="1">
+      <c r="A5" s="91">
         <v>6487</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="122">
+      <c r="D5" s="82">
         <v>3092009</v>
       </c>
-      <c r="E5" s="112" t="s">
+      <c r="E5" s="75" t="s">
         <v>36</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -1561,30 +1668,29 @@
       <c r="J5" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="111">
+      <c r="K5" s="65">
         <v>0.5</v>
       </c>
       <c r="L5" s="35" t="s">
         <v>39</v>
       </c>
       <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
+      <c r="N5" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-    </row>
-    <row r="6" spans="1:24" ht="45" customHeight="1">
-      <c r="A6" s="35"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="112" t="s">
+    </row>
+    <row r="6" spans="1:23" ht="45" customHeight="1">
+      <c r="A6" s="92"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="75" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -1593,7 +1699,7 @@
       <c r="G6" s="9">
         <v>0</v>
       </c>
-      <c r="H6" s="113">
+      <c r="H6" s="67">
         <v>531628</v>
       </c>
       <c r="I6" s="9"/>
@@ -1601,23 +1707,22 @@
       <c r="K6" s="9"/>
       <c r="L6" s="35"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
+      <c r="N6" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-    </row>
-    <row r="7" spans="1:24" s="51" customFormat="1" ht="90" customHeight="1">
-      <c r="A7" s="35"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="112" t="s">
+    </row>
+    <row r="7" spans="1:23" s="51" customFormat="1" ht="90" customHeight="1">
+      <c r="A7" s="92"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="75" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -1633,30 +1738,29 @@
       <c r="J7" s="35"/>
       <c r="K7" s="9"/>
       <c r="L7" s="35"/>
-      <c r="M7" s="114"/>
-      <c r="N7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-    </row>
-    <row r="8" spans="1:24" ht="60.75">
-      <c r="A8" s="123" t="s">
+    </row>
+    <row r="8" spans="1:23" ht="45.75">
+      <c r="A8" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="121"/>
-      <c r="D8" s="122">
+      <c r="C8" s="83"/>
+      <c r="D8" s="82">
         <v>4250000</v>
       </c>
-      <c r="E8" s="112" t="s">
+      <c r="E8" s="75" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -1674,28 +1778,27 @@
       <c r="J8" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="111">
+      <c r="K8" s="65">
         <v>0.3</v>
       </c>
-      <c r="L8" s="121"/>
+      <c r="L8" s="72"/>
       <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
+      <c r="N8" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:24" ht="60.75">
-      <c r="A9" s="123"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="112" t="s">
+    </row>
+    <row r="9" spans="1:23" ht="45.75">
+      <c r="A9" s="97"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="75" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="40" t="s">
@@ -1710,25 +1813,24 @@
       <c r="I9" s="9"/>
       <c r="J9" s="40"/>
       <c r="K9" s="9"/>
-      <c r="L9" s="121"/>
+      <c r="L9" s="72"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+      <c r="N9" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-    </row>
-    <row r="10" spans="1:24" ht="30.75">
-      <c r="A10" s="123"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="112" t="s">
+    </row>
+    <row r="10" spans="1:23" ht="30.75">
+      <c r="A10" s="97"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="75" t="s">
         <v>49</v>
       </c>
       <c r="F10" s="41" t="s">
@@ -1741,21 +1843,20 @@
       <c r="I10" s="9"/>
       <c r="J10" s="40"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="121"/>
+      <c r="L10" s="72"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-    </row>
-    <row r="11" spans="1:24" ht="60.75">
-      <c r="A11" s="35"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="112" t="s">
+    </row>
+    <row r="11" spans="1:23" ht="60.75">
+      <c r="A11" s="92"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="75" t="s">
         <v>52</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -1770,25 +1871,24 @@
       <c r="I11" s="9"/>
       <c r="J11" s="40"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="121"/>
+      <c r="L11" s="72"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
+      <c r="N11" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-    </row>
-    <row r="12" spans="1:24" ht="75" customHeight="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="112" t="s">
+    </row>
+    <row r="12" spans="1:23" ht="75" customHeight="1">
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="75" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="9" t="s">
@@ -1802,28 +1902,27 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="40"/>
-      <c r="K12" s="111">
+      <c r="K12" s="65">
         <v>0.3</v>
       </c>
-      <c r="L12" s="121"/>
+      <c r="L12" s="72"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
+      <c r="N12" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-    </row>
-    <row r="13" spans="1:24" ht="91.5">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="112" t="s">
+    </row>
+    <row r="13" spans="1:23" ht="91.5">
+      <c r="A13" s="92"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="75" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="9" t="s">
@@ -1835,28 +1934,27 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="40"/>
-      <c r="K13" s="111">
+      <c r="K13" s="65">
         <v>0.3</v>
       </c>
-      <c r="L13" s="121"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
+      <c r="N13" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P13" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-    </row>
-    <row r="14" spans="1:24" ht="90" customHeight="1">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="112" t="s">
+    </row>
+    <row r="14" spans="1:23" ht="90" customHeight="1">
+      <c r="A14" s="93"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="75" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -1870,34 +1968,33 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="40"/>
-      <c r="K14" s="111">
+      <c r="K14" s="65">
         <v>0.1</v>
       </c>
-      <c r="L14" s="121"/>
+      <c r="L14" s="72"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
+      <c r="N14" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P14" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-    </row>
-    <row r="15" spans="1:24" ht="60.75">
-      <c r="A15" s="115">
+    </row>
+    <row r="15" spans="1:23" ht="60.75">
+      <c r="A15" s="100">
         <v>125754</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="109">
+      <c r="C15" s="101"/>
+      <c r="D15" s="102">
         <v>55000</v>
       </c>
-      <c r="E15" s="112" t="s">
+      <c r="E15" s="66" t="s">
         <v>56</v>
       </c>
       <c r="F15" s="9" t="s">
@@ -1915,40 +2012,41 @@
       <c r="J15" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="111">
+      <c r="K15" s="65">
         <v>0.5</v>
       </c>
       <c r="L15" s="40" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
+      <c r="N15" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P15" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-    </row>
-    <row r="16" spans="1:24" ht="30" customHeight="1">
-      <c r="A16" s="123" t="s">
+    </row>
+    <row r="16" spans="1:23" ht="30" customHeight="1">
+      <c r="A16" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="122">
+      <c r="C16" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="82">
         <v>11182694</v>
       </c>
-      <c r="E16" s="116" t="s">
+      <c r="E16" s="98" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
@@ -1957,31 +2055,30 @@
         <v>4449727</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="35" t="s">
         <v>48</v>
       </c>
       <c r="K16" s="9"/>
-      <c r="L16" s="121"/>
+      <c r="L16" s="72"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
+      <c r="N16" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-    </row>
-    <row r="17" spans="1:19" ht="60.75">
-      <c r="A17" s="123"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="116" t="s">
+    </row>
+    <row r="17" spans="1:18" ht="45.75">
+      <c r="A17" s="97"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="98" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="40" t="s">
@@ -1996,62 +2093,60 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="121"/>
+      <c r="L17" s="72"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
+      <c r="N17" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-    </row>
-    <row r="18" spans="1:19" ht="60.75">
-      <c r="A18" s="123"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="116" t="s">
+    </row>
+    <row r="18" spans="1:18" ht="45.75">
+      <c r="A18" s="97"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="98" t="s">
         <v>49</v>
       </c>
       <c r="F18" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="117">
+      <c r="G18" s="69">
         <v>0</v>
       </c>
       <c r="H18" s="41"/>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="121"/>
+      <c r="L18" s="72"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
+      <c r="N18" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P18" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-    </row>
-    <row r="19" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A19" s="123"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="118" t="s">
-        <v>66</v>
+    </row>
+    <row r="19" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A19" s="97"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="99" t="s">
+        <v>67</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="119">
+        <v>68</v>
+      </c>
+      <c r="G19" s="71">
         <v>0</v>
       </c>
       <c r="H19" s="49">
@@ -2059,32 +2154,31 @@
       </c>
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="119"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-    </row>
-    <row r="20" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A20" s="123"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="118" t="s">
-        <v>68</v>
+    </row>
+    <row r="20" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A20" s="97"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="99" t="s">
+        <v>69</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="119">
+        <v>70</v>
+      </c>
+      <c r="G20" s="71">
         <v>0</v>
       </c>
       <c r="H20" s="49">
@@ -2092,32 +2186,31 @@
       </c>
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="119"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-    </row>
-    <row r="21" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A21" s="123"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="118" t="s">
+    </row>
+    <row r="21" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A21" s="97"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="99" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="119">
+        <v>71</v>
+      </c>
+      <c r="G21" s="71">
         <v>0</v>
       </c>
       <c r="H21" s="49">
@@ -2125,32 +2218,31 @@
       </c>
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="120"/>
-      <c r="N21" s="119"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P21" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-    </row>
-    <row r="22" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A22" s="123"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="118" t="s">
-        <v>71</v>
+    </row>
+    <row r="22" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A22" s="97"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="99" t="s">
+        <v>72</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="119">
+        <v>73</v>
+      </c>
+      <c r="G22" s="71">
         <v>0</v>
       </c>
       <c r="H22" s="49">
@@ -2158,32 +2250,31 @@
       </c>
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="119"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-    </row>
-    <row r="23" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A23" s="123"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="118" t="s">
+    </row>
+    <row r="23" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A23" s="103"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="99" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="119">
+        <v>74</v>
+      </c>
+      <c r="G23" s="71">
         <v>0</v>
       </c>
       <c r="H23" s="49">
@@ -2191,102 +2282,99 @@
       </c>
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="119"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-    </row>
-    <row r="24" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A24" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="35" t="s">
+    </row>
+    <row r="24" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A24" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="122">
+      <c r="B24" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="78"/>
+      <c r="D24" s="79">
         <v>6148000</v>
       </c>
-      <c r="E24" s="118" t="s">
+      <c r="E24" s="70" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="119">
+        <v>77</v>
+      </c>
+      <c r="G24" s="71">
         <v>0</v>
       </c>
       <c r="H24" s="49">
         <v>100</v>
       </c>
-      <c r="I24" s="119"/>
+      <c r="I24" s="71"/>
       <c r="J24" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="K24" s="119"/>
+        <v>78</v>
+      </c>
+      <c r="K24" s="71"/>
       <c r="L24" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="120"/>
-      <c r="N24" s="119"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-    </row>
-    <row r="25" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A25" s="123"/>
+    </row>
+    <row r="25" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A25" s="74"/>
       <c r="B25" s="35"/>
       <c r="C25" s="35"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="118" t="s">
-        <v>71</v>
+      <c r="D25" s="73"/>
+      <c r="E25" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="119">
+        <v>73</v>
+      </c>
+      <c r="G25" s="71">
         <v>0</v>
       </c>
       <c r="H25" s="49">
         <v>1000</v>
       </c>
-      <c r="I25" s="119"/>
+      <c r="I25" s="71"/>
       <c r="J25" s="35"/>
-      <c r="K25" s="119"/>
+      <c r="K25" s="71"/>
       <c r="L25" s="35"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="119"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P25" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-    </row>
-    <row r="26" spans="1:19" ht="60.75">
-      <c r="A26" s="123"/>
+    </row>
+    <row r="26" spans="1:18" ht="45.75">
+      <c r="A26" s="74"/>
       <c r="B26" s="35"/>
       <c r="C26" s="35"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="116" t="s">
+      <c r="D26" s="73"/>
+      <c r="E26" s="68" t="s">
         <v>49</v>
       </c>
       <c r="F26" s="40" t="s">
@@ -2302,26 +2390,25 @@
       <c r="J26" s="35"/>
       <c r="K26" s="9"/>
       <c r="L26" s="35"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-    </row>
-    <row r="27" spans="1:19" ht="60.75">
-      <c r="A27" s="123"/>
+    </row>
+    <row r="27" spans="1:18" ht="45.75">
+      <c r="A27" s="74"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="116"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="68"/>
       <c r="F27" s="41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" s="9">
         <v>0</v>
@@ -2333,75 +2420,74 @@
       <c r="J27" s="35"/>
       <c r="K27" s="9"/>
       <c r="L27" s="35"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P27" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-    </row>
-    <row r="28" spans="1:19" s="51" customFormat="1" ht="60.75">
-      <c r="A28" s="123"/>
+    </row>
+    <row r="28" spans="1:18" s="51" customFormat="1" ht="45.75">
+      <c r="A28" s="74"/>
       <c r="B28" s="35"/>
       <c r="C28" s="35"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="118" t="s">
+      <c r="D28" s="73"/>
+      <c r="E28" s="70" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" s="119">
+        <v>74</v>
+      </c>
+      <c r="G28" s="71">
         <v>0</v>
       </c>
       <c r="H28" s="49">
         <v>10000</v>
       </c>
-      <c r="I28" s="119"/>
+      <c r="I28" s="71"/>
       <c r="J28" s="35"/>
-      <c r="K28" s="119"/>
+      <c r="K28" s="71"/>
       <c r="L28" s="35"/>
-      <c r="M28" s="120"/>
-      <c r="N28" s="119"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="O28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-    </row>
-    <row r="30" spans="1:19">
+    </row>
+    <row r="30" spans="1:18">
       <c r="B30" s="31"/>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S28" xr:uid="{DAAB9C80-7A1B-4063-92E7-5EF52B20E471}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R28" xr:uid="{DAAB9C80-7A1B-4063-92E7-5EF52B20E471}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R28" xr:uid="{6F5BAC5B-A99A-4E0A-AEF4-19D7475FE8DB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q28" xr:uid="{6F5BAC5B-A99A-4E0A-AEF4-19D7475FE8DB}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q28" xr:uid="{330974BA-874B-4A57-BA48-69CDDAE39E8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P28" xr:uid="{330974BA-874B-4A57-BA48-69CDDAE39E8E}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P28" xr:uid="{75AA1A77-F052-4712-B65A-7280F7690744}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O28" xr:uid="{75AA1A77-F052-4712-B65A-7280F7690744}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O28" xr:uid="{CA28DAF7-343D-423E-A292-3196906C7FE3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N28" xr:uid="{CA28DAF7-343D-423E-A292-3196906C7FE3}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{236AB2E8-53E8-4198-A50E-49F32CD7DDE7}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{1C062E36-9485-4A01-836F-6A71BF34358F}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{F39CF8CF-610C-44AF-959E-FB723A0F0E58}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2463,7 +2549,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>13</v>
@@ -2532,14 +2618,14 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="45.75">
-      <c r="A3" s="74">
+      <c r="A3" s="110">
         <v>122627</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="70">
+      <c r="C3" s="111"/>
+      <c r="D3" s="108">
         <v>922000</v>
       </c>
       <c r="E3" s="55" t="s">
@@ -2554,16 +2640,16 @@
       <c r="H3" s="9">
         <v>1500</v>
       </c>
-      <c r="I3" s="75" t="s">
+      <c r="I3" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="109" t="s">
         <v>30</v>
       </c>
       <c r="K3" s="45">
         <v>0.5</v>
       </c>
-      <c r="L3" s="66"/>
+      <c r="L3" s="118"/>
       <c r="M3" s="19"/>
       <c r="O3" t="s">
         <v>25</v>
@@ -2573,10 +2659,10 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="121.5">
-      <c r="A4" s="74"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="70"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="108"/>
       <c r="E4" s="55" t="s">
         <v>31</v>
       </c>
@@ -2589,12 +2675,12 @@
       <c r="H4" s="9">
         <v>1000</v>
       </c>
-      <c r="I4" s="76"/>
-      <c r="J4" s="71"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="109"/>
       <c r="K4" s="45">
         <v>0.5</v>
       </c>
-      <c r="L4" s="68"/>
+      <c r="L4" s="120"/>
       <c r="M4" s="19"/>
       <c r="O4" t="s">
         <v>25</v>
@@ -2604,16 +2690,16 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="90" customHeight="1">
-      <c r="A5" s="62">
+      <c r="A5" s="105">
         <v>6487</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="108">
         <v>3092009</v>
       </c>
       <c r="E5" s="55" t="s">
@@ -2629,13 +2715,13 @@
         <v>2800</v>
       </c>
       <c r="I5" s="7"/>
-      <c r="J5" s="71" t="s">
+      <c r="J5" s="109" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="45">
         <v>0.5</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="115" t="s">
         <v>39</v>
       </c>
       <c r="M5" s="19"/>
@@ -2647,10 +2733,10 @@
       </c>
     </row>
     <row r="6" spans="1:24" ht="45" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="70"/>
+      <c r="A6" s="105"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
       <c r="E6" s="55" t="s">
         <v>40</v>
       </c>
@@ -2664,9 +2750,9 @@
         <v>531628</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="71"/>
+      <c r="J6" s="109"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="64"/>
+      <c r="L6" s="116"/>
       <c r="M6" s="19"/>
       <c r="O6" t="s">
         <v>25</v>
@@ -2676,10 +2762,10 @@
       </c>
     </row>
     <row r="7" spans="1:24" s="51" customFormat="1" ht="90" customHeight="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="70"/>
+      <c r="A7" s="105"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
       <c r="E7" s="55" t="s">
         <v>36</v>
       </c>
@@ -2693,9 +2779,9 @@
       <c r="I7" s="60">
         <v>106787</v>
       </c>
-      <c r="J7" s="71"/>
+      <c r="J7" s="109"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="65"/>
+      <c r="L7" s="117"/>
       <c r="M7" s="53"/>
       <c r="N7"/>
       <c r="O7" t="s">
@@ -2709,14 +2795,14 @@
       <c r="S7"/>
     </row>
     <row r="8" spans="1:24" ht="45.75">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="70">
+      <c r="C8" s="111"/>
+      <c r="D8" s="108">
         <v>4250000</v>
       </c>
       <c r="E8" s="55" t="s">
@@ -2734,13 +2820,13 @@
       <c r="I8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="73" t="s">
+      <c r="J8" s="107" t="s">
         <v>48</v>
       </c>
       <c r="K8" s="45">
         <v>0.3</v>
       </c>
-      <c r="L8" s="66"/>
+      <c r="L8" s="118"/>
       <c r="M8" s="19"/>
       <c r="O8" t="s">
         <v>25</v>
@@ -2750,10 +2836,10 @@
       </c>
     </row>
     <row r="9" spans="1:24" ht="30.75">
-      <c r="A9" s="69"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="70"/>
+      <c r="A9" s="114"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="108"/>
       <c r="E9" s="55" t="s">
         <v>49</v>
       </c>
@@ -2767,9 +2853,9 @@
         <v>4</v>
       </c>
       <c r="I9" s="9"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="107"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="67"/>
+      <c r="L9" s="119"/>
       <c r="M9" s="19"/>
       <c r="O9" t="s">
         <v>25</v>
@@ -2779,10 +2865,10 @@
       </c>
     </row>
     <row r="10" spans="1:24" ht="30.75">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="70"/>
+      <c r="A10" s="114"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="108"/>
       <c r="E10" s="55" t="s">
         <v>49</v>
       </c>
@@ -2794,16 +2880,16 @@
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="107"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="67"/>
+      <c r="L10" s="119"/>
       <c r="M10" s="19"/>
     </row>
     <row r="11" spans="1:24" ht="60.75">
-      <c r="A11" s="62"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="70"/>
+      <c r="A11" s="105"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="108"/>
       <c r="E11" s="55" t="s">
         <v>52</v>
       </c>
@@ -2817,9 +2903,9 @@
         <v>10</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="73"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="67"/>
+      <c r="L11" s="119"/>
       <c r="M11" s="19"/>
       <c r="O11" t="s">
         <v>25</v>
@@ -2829,10 +2915,10 @@
       </c>
     </row>
     <row r="12" spans="1:24" ht="75" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="70"/>
+      <c r="A12" s="105"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="108"/>
       <c r="E12" s="55" t="s">
         <v>31</v>
       </c>
@@ -2846,11 +2932,11 @@
         <v>55000</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="73"/>
+      <c r="J12" s="107"/>
       <c r="K12" s="45">
         <v>0.3</v>
       </c>
-      <c r="L12" s="67"/>
+      <c r="L12" s="119"/>
       <c r="M12" s="19"/>
       <c r="O12" t="s">
         <v>25</v>
@@ -2860,10 +2946,10 @@
       </c>
     </row>
     <row r="13" spans="1:24" ht="91.5">
-      <c r="A13" s="62"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="70"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="108"/>
       <c r="E13" s="55" t="s">
         <v>31</v>
       </c>
@@ -2875,11 +2961,11 @@
         <v>5</v>
       </c>
       <c r="I13" s="7"/>
-      <c r="J13" s="73"/>
+      <c r="J13" s="107"/>
       <c r="K13" s="45">
         <v>0.3</v>
       </c>
-      <c r="L13" s="67"/>
+      <c r="L13" s="119"/>
       <c r="M13" s="19"/>
       <c r="O13" t="s">
         <v>25</v>
@@ -2889,10 +2975,10 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="90" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="70"/>
+      <c r="A14" s="105"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="108"/>
       <c r="E14" s="55" t="s">
         <v>56</v>
       </c>
@@ -2906,11 +2992,11 @@
         <v>120</v>
       </c>
       <c r="I14" s="7"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="107"/>
       <c r="K14" s="45">
         <v>0.1</v>
       </c>
-      <c r="L14" s="68"/>
+      <c r="L14" s="120"/>
       <c r="M14" s="19"/>
       <c r="O14" t="s">
         <v>25</v>
@@ -2963,21 +3049,21 @@
       </c>
     </row>
     <row r="16" spans="1:24" ht="30" customHeight="1">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="62"/>
-      <c r="D16" s="70">
+      <c r="C16" s="105"/>
+      <c r="D16" s="108">
         <v>11182694</v>
       </c>
       <c r="E16" s="56" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="7">
         <v>0</v>
@@ -2985,14 +3071,14 @@
       <c r="H16" s="36">
         <v>4449727</v>
       </c>
-      <c r="I16" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" s="62" t="s">
+      <c r="I16" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="105" t="s">
         <v>48</v>
       </c>
       <c r="K16" s="7"/>
-      <c r="L16" s="66"/>
+      <c r="L16" s="118"/>
       <c r="M16" s="19"/>
       <c r="O16" t="s">
         <v>25</v>
@@ -3002,10 +3088,10 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="30.75">
-      <c r="A17" s="69"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="70"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="108"/>
       <c r="E17" s="56" t="s">
         <v>49</v>
       </c>
@@ -3018,10 +3104,10 @@
       <c r="H17" s="36">
         <v>8</v>
       </c>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="67"/>
+      <c r="L17" s="119"/>
       <c r="M17" s="19"/>
       <c r="O17" t="s">
         <v>25</v>
@@ -3031,10 +3117,10 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="30.75">
-      <c r="A18" s="69"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="70"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="108"/>
       <c r="E18" s="56" t="s">
         <v>49</v>
       </c>
@@ -3045,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="67"/>
+      <c r="L18" s="119"/>
       <c r="M18" s="19"/>
       <c r="O18" t="s">
         <v>25</v>
@@ -3058,15 +3144,15 @@
       </c>
     </row>
     <row r="19" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A19" s="69"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="70"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="108"/>
       <c r="E19" s="57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="50">
         <v>0</v>
@@ -3074,10 +3160,10 @@
       <c r="H19" s="48">
         <v>65</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
       <c r="K19" s="50"/>
-      <c r="L19" s="67"/>
+      <c r="L19" s="119"/>
       <c r="M19" s="52"/>
       <c r="O19" t="s">
         <v>25</v>
@@ -3090,15 +3176,15 @@
       <c r="S19"/>
     </row>
     <row r="20" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A20" s="69"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="70"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="50">
         <v>0</v>
@@ -3106,10 +3192,10 @@
       <c r="H20" s="48">
         <v>42</v>
       </c>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
       <c r="K20" s="50"/>
-      <c r="L20" s="67"/>
+      <c r="L20" s="119"/>
       <c r="M20" s="52"/>
       <c r="O20" t="s">
         <v>25</v>
@@ -3122,15 +3208,15 @@
       <c r="S20"/>
     </row>
     <row r="21" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A21" s="69"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="70"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="108"/>
       <c r="E21" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="50">
         <v>0</v>
@@ -3138,10 +3224,10 @@
       <c r="H21" s="48">
         <v>17</v>
       </c>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
       <c r="K21" s="50"/>
-      <c r="L21" s="67"/>
+      <c r="L21" s="119"/>
       <c r="M21" s="52"/>
       <c r="O21" t="s">
         <v>25</v>
@@ -3154,15 +3240,15 @@
       <c r="S21"/>
     </row>
     <row r="22" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A22" s="69"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="70"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="108"/>
       <c r="E22" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" s="50">
         <v>0</v>
@@ -3170,10 +3256,10 @@
       <c r="H22" s="48">
         <v>113</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
       <c r="K22" s="50"/>
-      <c r="L22" s="67"/>
+      <c r="L22" s="119"/>
       <c r="M22" s="52"/>
       <c r="O22" t="s">
         <v>25</v>
@@ -3186,15 +3272,15 @@
       <c r="S22"/>
     </row>
     <row r="23" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A23" s="69"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="70"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="108"/>
       <c r="E23" s="57" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="50">
         <v>0</v>
@@ -3202,10 +3288,10 @@
       <c r="H23" s="48">
         <v>3001</v>
       </c>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
       <c r="K23" s="50"/>
-      <c r="L23" s="68"/>
+      <c r="L23" s="120"/>
       <c r="M23" s="52"/>
       <c r="O23" t="s">
         <v>25</v>
@@ -3218,21 +3304,21 @@
       <c r="S23"/>
     </row>
     <row r="24" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A24" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="62" t="s">
+      <c r="A24" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="62"/>
-      <c r="D24" s="70">
+      <c r="B24" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="105"/>
+      <c r="D24" s="108">
         <v>6148000</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="50">
         <v>0</v>
@@ -3241,11 +3327,11 @@
         <v>100</v>
       </c>
       <c r="I24" s="50"/>
-      <c r="J24" s="62" t="s">
-        <v>77</v>
+      <c r="J24" s="105" t="s">
+        <v>78</v>
       </c>
       <c r="K24" s="50"/>
-      <c r="L24" s="63" t="s">
+      <c r="L24" s="115" t="s">
         <v>24</v>
       </c>
       <c r="M24" s="52"/>
@@ -3260,15 +3346,15 @@
       <c r="S24"/>
     </row>
     <row r="25" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A25" s="69"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="70"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="108"/>
       <c r="E25" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" s="50">
         <v>0</v>
@@ -3277,9 +3363,9 @@
         <v>1000</v>
       </c>
       <c r="I25" s="50"/>
-      <c r="J25" s="62"/>
+      <c r="J25" s="105"/>
       <c r="K25" s="50"/>
-      <c r="L25" s="64"/>
+      <c r="L25" s="116"/>
       <c r="M25" s="52"/>
       <c r="O25" t="s">
         <v>25</v>
@@ -3292,10 +3378,10 @@
       <c r="S25"/>
     </row>
     <row r="26" spans="1:19" ht="30.75">
-      <c r="A26" s="69"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="70"/>
+      <c r="A26" s="114"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="108"/>
       <c r="E26" s="56" t="s">
         <v>49</v>
       </c>
@@ -3309,9 +3395,9 @@
         <v>2</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="62"/>
+      <c r="J26" s="105"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="64"/>
+      <c r="L26" s="116"/>
       <c r="M26" s="53"/>
       <c r="O26" t="s">
         <v>25</v>
@@ -3321,13 +3407,13 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="69"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="70"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="108"/>
       <c r="E27" s="56"/>
       <c r="F27" s="41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" s="7">
         <v>0</v>
@@ -3336,9 +3422,9 @@
         <v>0.4</v>
       </c>
       <c r="I27" s="7"/>
-      <c r="J27" s="62"/>
+      <c r="J27" s="105"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="64"/>
+      <c r="L27" s="116"/>
       <c r="M27" s="53"/>
       <c r="O27" t="s">
         <v>25</v>
@@ -3348,15 +3434,15 @@
       </c>
     </row>
     <row r="28" spans="1:19" s="51" customFormat="1" ht="30.75">
-      <c r="A28" s="69"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="70"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="57" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G28" s="50">
         <v>0</v>
@@ -3365,9 +3451,9 @@
         <v>10000</v>
       </c>
       <c r="I28" s="50"/>
-      <c r="J28" s="62"/>
+      <c r="J28" s="105"/>
       <c r="K28" s="50"/>
-      <c r="L28" s="65"/>
+      <c r="L28" s="117"/>
       <c r="M28" s="52"/>
       <c r="O28" t="s">
         <v>25</v>
@@ -3384,38 +3470,38 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J16:J23"/>
+    <mergeCell ref="L24:L28"/>
+    <mergeCell ref="L16:L23"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="L8:L14"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="B8:B14"/>
+    <mergeCell ref="C8:C14"/>
+    <mergeCell ref="D8:D14"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="I16:I23"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="C16:C23"/>
-    <mergeCell ref="D16:D23"/>
-    <mergeCell ref="I16:I23"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="B8:B14"/>
-    <mergeCell ref="C8:C14"/>
-    <mergeCell ref="D8:D14"/>
-    <mergeCell ref="J8:J14"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="J16:J23"/>
-    <mergeCell ref="L24:L28"/>
-    <mergeCell ref="L16:L23"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="L8:L14"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="J5:J7"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{4508A1F8-96DE-41B3-8189-7C0C3128B039}"/>
@@ -3513,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>22</v>
@@ -3523,14 +3609,14 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="60">
-      <c r="A3" s="81">
+      <c r="A3" s="128">
         <v>122627</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="85">
+      <c r="C3" s="111"/>
+      <c r="D3" s="132">
         <v>922000</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -3543,20 +3629,20 @@
         <v>0</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="95" t="s">
+      <c r="J3" s="142" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="121.5">
-      <c r="A4" s="82"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="87"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="134"/>
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
@@ -3567,24 +3653,24 @@
         <v>0</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4" s="95"/>
+        <v>83</v>
+      </c>
+      <c r="J4" s="142"/>
     </row>
     <row r="5" spans="1:14" ht="90" customHeight="1">
-      <c r="A5" s="63">
+      <c r="A5" s="115">
         <v>6487</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="132">
         <v>3092009</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -3597,62 +3683,62 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5" s="15"/>
-      <c r="J5" s="96" t="s">
+      <c r="J5" s="143" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="45" customHeight="1">
-      <c r="A6" s="64"/>
-      <c r="B6" s="90"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="86"/>
+      <c r="A6" s="116"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="133"/>
       <c r="E6" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="143"/>
+    </row>
+    <row r="7" spans="1:14" ht="90" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:14" ht="90" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="96"/>
+        <v>89</v>
+      </c>
+      <c r="J7" s="143"/>
     </row>
     <row r="8" spans="1:14" ht="45.75">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="85">
+      <c r="C8" s="118"/>
+      <c r="D8" s="132">
         <v>4250000</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -3665,20 +3751,20 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="97" t="s">
+      <c r="J8" s="124" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30.75">
-      <c r="A9" s="84"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="86"/>
+      <c r="A9" s="131"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="133"/>
       <c r="E9" s="7" t="s">
         <v>49</v>
       </c>
@@ -3692,15 +3778,15 @@
         <v>4</v>
       </c>
       <c r="I9" s="11"/>
-      <c r="J9" s="97"/>
+      <c r="J9" s="124"/>
     </row>
     <row r="10" spans="1:14" ht="30.75">
-      <c r="A10" s="84"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="86"/>
+      <c r="A10" s="131"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="133"/>
       <c r="E10" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10" s="33" t="s">
         <v>51</v>
@@ -3713,13 +3799,13 @@
         <v>6400</v>
       </c>
       <c r="I10" s="11"/>
-      <c r="J10" s="97"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:14" ht="60">
-      <c r="A11" s="64"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="86"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="133"/>
       <c r="E11" s="7" t="s">
         <v>52</v>
       </c>
@@ -3733,9 +3819,9 @@
         <v>10</v>
       </c>
       <c r="I11" s="11"/>
-      <c r="J11" s="97"/>
+      <c r="J11" s="124"/>
       <c r="L11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M11">
         <f>SUM(H9+H17+H26)</f>
@@ -3747,10 +3833,10 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="75">
-      <c r="A12" s="64"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="86"/>
+      <c r="A12" s="116"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="133"/>
       <c r="E12" s="7" t="s">
         <v>31</v>
       </c>
@@ -3761,12 +3847,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I12" s="18"/>
-      <c r="J12" s="97"/>
+      <c r="J12" s="124"/>
       <c r="L12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M12">
         <f>SUM(H10+H18+H27)</f>
@@ -3774,28 +3860,28 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="75">
-      <c r="A13" s="64"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="86"/>
+      <c r="A13" s="116"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="133"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I13" s="19"/>
-      <c r="J13" s="97"/>
+      <c r="J13" s="124"/>
     </row>
     <row r="14" spans="1:14" ht="90">
-      <c r="A14" s="64"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="87"/>
+      <c r="A14" s="116"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="134"/>
       <c r="E14" s="13" t="s">
         <v>56</v>
       </c>
@@ -3806,10 +3892,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I14" s="20"/>
-      <c r="J14" s="97"/>
+      <c r="J14" s="124"/>
     </row>
     <row r="15" spans="1:14" ht="60">
       <c r="A15" s="29">
@@ -3832,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" s="30" t="s">
         <v>60</v>
@@ -3842,21 +3928,21 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="30">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="98" t="s">
+      <c r="B16" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="98"/>
-      <c r="D16" s="99">
+      <c r="C16" s="123"/>
+      <c r="D16" s="122">
         <v>11182694</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="23">
         <v>0</v>
@@ -3864,18 +3950,18 @@
       <c r="H16" s="24">
         <v>4449727</v>
       </c>
-      <c r="I16" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" s="78" t="s">
+      <c r="I16" s="125" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="125" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30.75">
-      <c r="A17" s="100"/>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="99"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="122"/>
       <c r="E17" s="24" t="s">
         <v>49</v>
       </c>
@@ -3888,16 +3974,16 @@
       <c r="H17" s="24">
         <v>8</v>
       </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
     </row>
     <row r="18" spans="1:10" ht="30.75">
-      <c r="A18" s="100"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="99"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="122"/>
       <c r="E18" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="33" t="s">
         <v>51</v>
@@ -3909,19 +3995,19 @@
         <f>H17*1600</f>
         <v>12800</v>
       </c>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
     </row>
     <row r="19" spans="1:10" ht="30.75">
-      <c r="A19" s="100"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="99"/>
+      <c r="A19" s="121"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="122"/>
       <c r="E19" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="23">
         <v>0</v>
@@ -3929,19 +4015,19 @@
       <c r="H19" s="24">
         <v>65</v>
       </c>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
     </row>
     <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="100"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="99"/>
+      <c r="A20" s="121"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="122"/>
       <c r="E20" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="23">
         <v>0</v>
@@ -3949,19 +4035,19 @@
       <c r="H20" s="24">
         <v>42</v>
       </c>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="126"/>
     </row>
     <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="100"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="99"/>
+      <c r="A21" s="121"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="122"/>
       <c r="E21" s="24" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="23">
         <v>0</v>
@@ -3969,19 +4055,19 @@
       <c r="H21" s="24">
         <v>17</v>
       </c>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
     </row>
     <row r="22" spans="1:10" ht="30">
-      <c r="A22" s="100"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="99"/>
+      <c r="A22" s="121"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="122"/>
       <c r="E22" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" s="23">
         <v>0</v>
@@ -3989,19 +4075,19 @@
       <c r="H22" s="24">
         <v>113</v>
       </c>
-      <c r="I22" s="79"/>
-      <c r="J22" s="79"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="126"/>
     </row>
     <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="100"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="99"/>
+      <c r="A23" s="121"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="122"/>
       <c r="E23" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="23">
         <v>0</v>
@@ -4009,25 +4095,25 @@
       <c r="H23" s="24">
         <v>3001</v>
       </c>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="98" t="s">
+      <c r="A24" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="98"/>
-      <c r="D24" s="99">
+      <c r="B24" s="123" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="123"/>
+      <c r="D24" s="122">
         <v>6148000</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="23">
         <v>0</v>
@@ -4036,20 +4122,20 @@
         <v>100</v>
       </c>
       <c r="I24" s="23"/>
-      <c r="J24" s="78" t="s">
-        <v>77</v>
+      <c r="J24" s="125" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="100"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="99"/>
+      <c r="A25" s="121"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="122"/>
       <c r="E25" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" s="23">
         <v>0</v>
@@ -4058,13 +4144,13 @@
         <v>2</v>
       </c>
       <c r="I25" s="23"/>
-      <c r="J25" s="79"/>
+      <c r="J25" s="126"/>
     </row>
     <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="100"/>
-      <c r="B26" s="98"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="99"/>
+      <c r="A26" s="121"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="122"/>
       <c r="E26" s="24" t="s">
         <v>49</v>
       </c>
@@ -4078,15 +4164,15 @@
         <v>2</v>
       </c>
       <c r="I26" s="23"/>
-      <c r="J26" s="79"/>
+      <c r="J26" s="126"/>
     </row>
     <row r="27" spans="1:10" ht="30.75">
-      <c r="A27" s="100"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="99"/>
+      <c r="A27" s="121"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="122"/>
       <c r="E27" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" s="33" t="s">
         <v>51</v>
@@ -4099,18 +4185,18 @@
         <v>3200</v>
       </c>
       <c r="I27" s="23"/>
-      <c r="J27" s="79"/>
+      <c r="J27" s="126"/>
     </row>
     <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="100"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="99"/>
+      <c r="A28" s="121"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="122"/>
       <c r="E28" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G28" s="23">
         <v>0</v>
@@ -4119,7 +4205,7 @@
         <v>10000</v>
       </c>
       <c r="I28" s="23"/>
-      <c r="J28" s="80"/>
+      <c r="J28" s="127"/>
     </row>
     <row r="30" spans="1:10">
       <c r="B30" s="31"/>
@@ -4132,16 +4218,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="J8:J14"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="C16:C23"/>
-    <mergeCell ref="D16:D23"/>
-    <mergeCell ref="J16:J23"/>
     <mergeCell ref="J24:J28"/>
     <mergeCell ref="I16:I23"/>
     <mergeCell ref="A3:A4"/>
@@ -4158,6 +4234,16 @@
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="J16:J23"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4188,160 +4274,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="101" t="s">
-        <v>98</v>
+      <c r="A2" s="144" t="s">
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="101"/>
+      <c r="A3" s="144"/>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="101"/>
+      <c r="A4" s="144"/>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="102" t="s">
-        <v>103</v>
+      <c r="A5" s="145" t="s">
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="102"/>
+      <c r="A6" s="145"/>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="102"/>
+      <c r="A7" s="145"/>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="102"/>
+      <c r="A8" s="145"/>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="102"/>
+      <c r="A9" s="145"/>
       <c r="B9" t="s">
         <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="103" t="s">
-        <v>109</v>
+      <c r="A10" s="146" t="s">
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="103"/>
+      <c r="A11" s="146"/>
       <c r="B11" t="s">
         <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="104" t="s">
-        <v>113</v>
+      <c r="A12" s="147" t="s">
+        <v>115</v>
       </c>
       <c r="B12" t="s">
         <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="104"/>
+      <c r="A13" s="147"/>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="104"/>
+      <c r="A14" s="147"/>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -4365,29 +4451,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Mamunur Rashid</DisplayName>
-        <AccountId>1909</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mohammed Faez issa Al-Attar</DisplayName>
-        <AccountId>1316</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -4636,14 +4699,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Mamunur Rashid</DisplayName>
+        <AccountId>1909</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mohammed Faez issa Al-Attar</DisplayName>
+        <AccountId>1316</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B2F36C-ED54-4CE9-938D-170704522F69}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D725300-A553-47A2-B3D8-21DC5742429F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749CB1BA-1022-4E25-B9B0-E9E22067111A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749CB1BA-1022-4E25-B9B0-E9E22067111A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D725300-A553-47A2-B3D8-21DC5742429F}"/>
 </file>
--- a/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28502"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="633" documentId="11_13400C8A471826D5940B628CA6FCA9A8E4E8ED3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F4BB4D-743C-41BC-8ECF-EEF74610D752}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="11_13400C8A471826D5940B628CA6FCA9A8E4E8ED3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{201DD796-E186-432E-96BE-E7D83036EC3E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="145">
   <si>
     <t>Project ID</t>
   </si>
@@ -104,6 +104,9 @@
     <t>Policy Population</t>
   </si>
   <si>
+    <t>project document</t>
+  </si>
+  <si>
     <t>Climate Action for Human Security (Regional project component)</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
   <si>
     <t xml:space="preserve">Climate Action for Human Security </t>
@@ -156,7 +162,7 @@
     <t>Promoting Carbon Reduction Through Energy Efficiency (EE) Techniques in Iraq</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=6487</t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -308,6 +314,9 @@
     <t>Energy Infrastructure Services</t>
   </si>
   <si>
+    <t xml:space="preserve">Total of  MW solar energy added </t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -315,6 +324,9 @@
   </si>
   <si>
     <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -487,7 +499,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,8 +559,30 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,6 +611,16 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -750,14 +794,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1021,9 +1068,48 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1042,32 +1128,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1126,17 +1197,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1148,8 +1210,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="5">
+    <cellStyle name="Bueno" xfId="2" builtinId="26"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="4" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1475,7 +1540,7 @@
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75">
+    <row r="1" spans="1:23" ht="45">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -1539,27 +1604,29 @@
       <c r="U1" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1"/>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23" ht="45.75">
+    <row r="2" spans="1:23" ht="47.1" customHeight="1">
       <c r="A2" s="11">
         <v>122659</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="62">
         <v>149000</v>
       </c>
       <c r="E2" s="63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
@@ -1568,20 +1635,20 @@
         <v>1500</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="64">
         <v>0.5</v>
       </c>
       <c r="L2" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="25"/>
       <c r="N2" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="25"/>
       <c r="P2" s="25"/>
@@ -1590,23 +1657,26 @@
       <c r="S2" s="33"/>
       <c r="T2" s="25"/>
       <c r="U2" s="33"/>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:23" ht="45.75">
       <c r="A3" s="65">
         <v>122627</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="67"/>
       <c r="D3" s="68">
         <v>922000</v>
       </c>
       <c r="E3" s="69" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -1615,41 +1685,41 @@
         <v>1500</v>
       </c>
       <c r="I3" s="70" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K3" s="64">
         <v>0.5</v>
       </c>
       <c r="L3" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="25"/>
       <c r="N3" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="25"/>
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
       <c r="S3" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T3" s="25"/>
       <c r="U3" s="33"/>
     </row>
-    <row r="4" spans="1:23" ht="121.5">
+    <row r="4" spans="1:23" ht="135">
       <c r="A4" s="71"/>
       <c r="B4" s="72"/>
       <c r="C4" s="73"/>
       <c r="D4" s="74"/>
       <c r="E4" s="69" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -1663,11 +1733,11 @@
         <v>0.5</v>
       </c>
       <c r="L4" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" s="25"/>
       <c r="N4" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="25"/>
       <c r="P4" s="25"/>
@@ -1682,19 +1752,19 @@
         <v>6487</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="66" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="C5" s="146" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="68">
         <v>3092009</v>
       </c>
       <c r="E5" s="69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1704,17 +1774,17 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K5" s="64">
         <v>0.5</v>
       </c>
       <c r="L5" s="100" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M5" s="25"/>
       <c r="N5" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O5" s="25"/>
       <c r="P5" s="25"/>
@@ -1724,7 +1794,7 @@
       <c r="T5" s="25"/>
       <c r="U5" s="33"/>
     </row>
-    <row r="6" spans="1:23" ht="167.25">
+    <row r="6" spans="1:23" ht="210">
       <c r="A6" s="71"/>
       <c r="B6" s="76"/>
       <c r="C6" s="72"/>
@@ -1733,7 +1803,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -1743,21 +1813,21 @@
       <c r="L6" s="100"/>
       <c r="M6" s="25"/>
       <c r="N6" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P6" s="25"/>
       <c r="Q6" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R6" s="25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S6" s="33"/>
       <c r="T6" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U6" s="33">
         <v>274000</v>
@@ -1769,10 +1839,10 @@
       <c r="C7" s="72"/>
       <c r="D7" s="74"/>
       <c r="E7" s="69" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="6">
         <v>0</v>
@@ -1784,11 +1854,11 @@
       <c r="J7" s="32"/>
       <c r="K7" s="6"/>
       <c r="L7" s="100" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M7" s="25"/>
       <c r="N7" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
@@ -1798,16 +1868,16 @@
       <c r="T7" s="25"/>
       <c r="U7" s="33"/>
     </row>
-    <row r="8" spans="1:23" s="48" customFormat="1" ht="121.5">
+    <row r="8" spans="1:23" s="48" customFormat="1" ht="120">
       <c r="A8" s="71"/>
       <c r="B8" s="76"/>
       <c r="C8" s="72"/>
       <c r="D8" s="74"/>
       <c r="E8" s="69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
@@ -1819,11 +1889,11 @@
       <c r="J8" s="32"/>
       <c r="K8" s="6"/>
       <c r="L8" s="100" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M8" s="25"/>
       <c r="N8" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -1838,19 +1908,19 @@
         <v>85156</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" s="102" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="68">
         <v>4250000</v>
       </c>
       <c r="E9" s="69" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
@@ -1859,78 +1929,78 @@
         <v>400</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K9" s="64">
         <v>0.3</v>
       </c>
       <c r="L9" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M9" s="25"/>
       <c r="N9" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O9" s="25"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
       <c r="R9" s="25"/>
       <c r="S9" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="33"/>
     </row>
-    <row r="10" spans="1:23" ht="45.75">
+    <row r="10" spans="1:23" ht="45">
       <c r="A10" s="79"/>
       <c r="B10" s="71"/>
       <c r="C10" s="73"/>
       <c r="D10" s="74"/>
       <c r="E10" s="69" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="103">
         <v>4</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="37"/>
       <c r="K10" s="6"/>
       <c r="L10" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" s="25"/>
       <c r="N10" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O10" s="25"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
       <c r="R10" s="25"/>
       <c r="S10" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="33"/>
     </row>
-    <row r="11" spans="1:23" ht="45.75">
+    <row r="11" spans="1:23" ht="45">
       <c r="A11" s="79"/>
       <c r="B11" s="71"/>
       <c r="C11" s="73"/>
       <c r="D11" s="74"/>
       <c r="E11" s="69" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
@@ -1940,11 +2010,11 @@
       <c r="J11" s="37"/>
       <c r="K11" s="6"/>
       <c r="L11" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" s="25"/>
       <c r="N11" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O11" s="25"/>
       <c r="P11" s="25"/>
@@ -1954,32 +2024,32 @@
       <c r="T11" s="25"/>
       <c r="U11" s="33"/>
     </row>
-    <row r="12" spans="1:23" ht="60.75">
+    <row r="12" spans="1:23" ht="60">
       <c r="A12" s="71"/>
       <c r="B12" s="71"/>
       <c r="C12" s="73"/>
       <c r="D12" s="74"/>
       <c r="E12" s="69" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="106">
         <v>10</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="37"/>
       <c r="K12" s="6"/>
       <c r="L12" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" s="25"/>
       <c r="N12" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
@@ -1995,10 +2065,10 @@
       <c r="C13" s="73"/>
       <c r="D13" s="74"/>
       <c r="E13" s="69" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>
@@ -2012,11 +2082,11 @@
         <v>0.3</v>
       </c>
       <c r="L13" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
@@ -2026,16 +2096,16 @@
       <c r="T13" s="25"/>
       <c r="U13" s="33"/>
     </row>
-    <row r="14" spans="1:23" ht="91.5">
+    <row r="14" spans="1:23" ht="90">
       <c r="A14" s="71"/>
       <c r="B14" s="71"/>
       <c r="C14" s="73"/>
       <c r="D14" s="74"/>
       <c r="E14" s="69" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6">
@@ -2047,11 +2117,11 @@
         <v>0.3</v>
       </c>
       <c r="L14" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M14" s="25"/>
       <c r="N14" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O14" s="25"/>
       <c r="P14" s="25"/>
@@ -2067,10 +2137,10 @@
       <c r="C15" s="81"/>
       <c r="D15" s="82"/>
       <c r="E15" s="69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
@@ -2084,11 +2154,11 @@
         <v>0.1</v>
       </c>
       <c r="L15" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M15" s="25"/>
       <c r="N15" s="101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
@@ -2103,17 +2173,17 @@
         <v>125754</v>
       </c>
       <c r="B16" s="83" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" s="84"/>
       <c r="D16" s="85">
         <v>55000</v>
       </c>
       <c r="E16" s="63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G16" s="6">
         <v>0</v>
@@ -2122,20 +2192,20 @@
         <v>200</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K16" s="64">
         <v>0.5</v>
       </c>
       <c r="L16" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M16" s="25"/>
       <c r="N16" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
@@ -2150,19 +2220,19 @@
         <v>89459</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" s="68">
         <v>11182694</v>
       </c>
       <c r="E17" s="87" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G17" s="6">
         <v>0</v>
@@ -2171,76 +2241,76 @@
         <v>4449727</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J17" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M17" s="25"/>
       <c r="N17" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O17" s="25"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25"/>
       <c r="S17" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T17" s="25"/>
       <c r="U17" s="33"/>
     </row>
-    <row r="18" spans="1:21" ht="45.75">
+    <row r="18" spans="1:21" ht="60">
       <c r="A18" s="79"/>
       <c r="B18" s="71"/>
       <c r="C18" s="71"/>
       <c r="D18" s="74"/>
       <c r="E18" s="87" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="104">
         <v>8</v>
       </c>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
       <c r="K18" s="6"/>
       <c r="L18" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M18" s="25"/>
       <c r="N18" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
       <c r="R18" s="25"/>
       <c r="S18" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="33"/>
     </row>
-    <row r="19" spans="1:21" ht="45.75">
+    <row r="19" spans="1:21" ht="60">
       <c r="A19" s="79"/>
       <c r="B19" s="71"/>
       <c r="C19" s="71"/>
       <c r="D19" s="74"/>
       <c r="E19" s="87" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G19" s="6">
         <v>0</v>
@@ -2250,32 +2320,32 @@
       <c r="J19" s="32"/>
       <c r="K19" s="6"/>
       <c r="L19" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M19" s="25"/>
       <c r="N19" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25"/>
       <c r="S19" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T19" s="25"/>
       <c r="U19" s="33"/>
     </row>
-    <row r="20" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="20" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A20" s="79"/>
       <c r="B20" s="71"/>
       <c r="C20" s="71"/>
       <c r="D20" s="74"/>
       <c r="E20" s="87" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G20" s="6">
         <v>0</v>
@@ -2287,11 +2357,11 @@
       <c r="J20" s="32"/>
       <c r="K20" s="6"/>
       <c r="L20" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M20" s="25"/>
       <c r="N20" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
@@ -2301,16 +2371,16 @@
       <c r="T20" s="25"/>
       <c r="U20" s="33"/>
     </row>
-    <row r="21" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="21" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A21" s="79"/>
       <c r="B21" s="71"/>
       <c r="C21" s="71"/>
       <c r="D21" s="74"/>
       <c r="E21" s="87" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -2322,11 +2392,11 @@
       <c r="J21" s="32"/>
       <c r="K21" s="6"/>
       <c r="L21" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M21" s="25"/>
       <c r="N21" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
@@ -2336,16 +2406,16 @@
       <c r="T21" s="25"/>
       <c r="U21" s="33"/>
     </row>
-    <row r="22" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="22" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A22" s="79"/>
       <c r="B22" s="71"/>
       <c r="C22" s="71"/>
       <c r="D22" s="74"/>
       <c r="E22" s="87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" s="6">
         <v>0</v>
@@ -2357,11 +2427,11 @@
       <c r="J22" s="32"/>
       <c r="K22" s="6"/>
       <c r="L22" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M22" s="25"/>
       <c r="N22" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
@@ -2371,16 +2441,16 @@
       <c r="T22" s="25"/>
       <c r="U22" s="33"/>
     </row>
-    <row r="23" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="23" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A23" s="79"/>
       <c r="B23" s="71"/>
       <c r="C23" s="71"/>
       <c r="D23" s="74"/>
       <c r="E23" s="87" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
@@ -2392,11 +2462,11 @@
       <c r="J23" s="32"/>
       <c r="K23" s="6"/>
       <c r="L23" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M23" s="25"/>
       <c r="N23" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
@@ -2406,16 +2476,16 @@
       <c r="T23" s="25"/>
       <c r="U23" s="33"/>
     </row>
-    <row r="24" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="24" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A24" s="88"/>
       <c r="B24" s="80"/>
       <c r="C24" s="80"/>
       <c r="D24" s="82"/>
       <c r="E24" s="87" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -2427,11 +2497,11 @@
       <c r="J24" s="32"/>
       <c r="K24" s="6"/>
       <c r="L24" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M24" s="25"/>
       <c r="N24" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
@@ -2446,17 +2516,17 @@
         <v>116195</v>
       </c>
       <c r="B25" s="90" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25" s="90"/>
       <c r="D25" s="82">
         <v>6148000</v>
       </c>
       <c r="E25" s="91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G25" s="6">
         <v>0</v>
@@ -2466,15 +2536,15 @@
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M25" s="25"/>
       <c r="N25" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
@@ -2484,16 +2554,16 @@
       <c r="T25" s="25"/>
       <c r="U25" s="33"/>
     </row>
-    <row r="26" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="26" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A26" s="92"/>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="93"/>
       <c r="E26" s="91" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
@@ -2505,11 +2575,11 @@
       <c r="J26" s="32"/>
       <c r="K26" s="6"/>
       <c r="L26" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M26" s="25"/>
       <c r="N26" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O26" s="25"/>
       <c r="P26" s="25"/>
@@ -2519,53 +2589,53 @@
       <c r="T26" s="25"/>
       <c r="U26" s="33"/>
     </row>
-    <row r="27" spans="1:21" ht="45.75">
+    <row r="27" spans="1:21" ht="60">
       <c r="A27" s="92"/>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
       <c r="D27" s="93"/>
       <c r="E27" s="91" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="104">
         <v>2</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="32"/>
       <c r="K27" s="6"/>
       <c r="L27" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M27" s="25"/>
       <c r="N27" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T27" s="25"/>
       <c r="U27" s="33"/>
     </row>
-    <row r="28" spans="1:21" ht="45.75">
+    <row r="28" spans="1:21" ht="60">
       <c r="A28" s="92"/>
       <c r="B28" s="32"/>
       <c r="C28" s="32"/>
       <c r="D28" s="93"/>
       <c r="E28" s="91" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G28" s="6">
         <v>0</v>
@@ -2577,32 +2647,32 @@
       <c r="J28" s="32"/>
       <c r="K28" s="6"/>
       <c r="L28" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M28" s="25"/>
       <c r="N28" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
       <c r="Q28" s="25"/>
       <c r="R28" s="25"/>
       <c r="S28" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T28" s="25"/>
       <c r="U28" s="33"/>
     </row>
-    <row r="29" spans="1:21" s="48" customFormat="1" ht="45.75">
+    <row r="29" spans="1:21" s="48" customFormat="1" ht="60">
       <c r="A29" s="92"/>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
       <c r="D29" s="93"/>
       <c r="E29" s="91" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G29" s="6">
         <v>0</v>
@@ -2614,11 +2684,11 @@
       <c r="J29" s="32"/>
       <c r="K29" s="6"/>
       <c r="L29" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M29" s="25"/>
       <c r="N29" s="101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O29" s="25"/>
       <c r="P29" s="25"/>
@@ -2628,8 +2698,15 @@
       <c r="T29" s="25"/>
       <c r="U29" s="33"/>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" ht="29.45" customHeight="1">
       <c r="B31" s="28"/>
+      <c r="G31" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31">
+        <f>SUM(H27,H18,H10)</f>
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="10">
@@ -2666,6 +2743,7 @@
     <hyperlink ref="C2" r:id="rId1" xr:uid="{1C062E36-9485-4A01-836F-6A71BF34358F}"/>
     <hyperlink ref="C17" r:id="rId2" xr:uid="{F39CF8CF-610C-44AF-959E-FB723A0F0E58}"/>
     <hyperlink ref="C9" r:id="rId3" xr:uid="{2A6D453A-73EB-4ED7-845F-F257ED017140}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{5395C8FA-D527-4079-B08A-41EE7FD37E4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2736,10 +2814,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -2762,24 +2840,24 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="30.75">
+    <row r="2" spans="1:24" ht="30">
       <c r="A2" s="25">
         <v>122659</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="23">
         <v>149000</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2788,41 +2866,41 @@
         <v>1500</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="42">
         <v>0.5</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="4"/>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="45.75">
-      <c r="A3" s="115">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="60">
+      <c r="A3" s="112">
         <v>122627</v>
       </c>
-      <c r="B3" s="114" t="s">
-        <v>29</v>
+      <c r="B3" s="109" t="s">
+        <v>31</v>
       </c>
       <c r="C3" s="113"/>
-      <c r="D3" s="111">
+      <c r="D3" s="110">
         <v>922000</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2830,34 +2908,34 @@
       <c r="H3" s="6">
         <v>1500</v>
       </c>
-      <c r="I3" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="112" t="s">
-        <v>33</v>
+      <c r="I3" s="114" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="111" t="s">
+        <v>35</v>
       </c>
       <c r="K3" s="42">
         <v>0.5</v>
       </c>
-      <c r="L3" s="107"/>
+      <c r="L3" s="120"/>
       <c r="M3" s="16"/>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="121.5">
-      <c r="A4" s="115"/>
-      <c r="B4" s="114"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="135">
+      <c r="A4" s="112"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="113"/>
-      <c r="D4" s="111"/>
+      <c r="D4" s="110"/>
       <c r="E4" s="52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2865,38 +2943,38 @@
       <c r="H4" s="6">
         <v>1000</v>
       </c>
-      <c r="I4" s="117"/>
-      <c r="J4" s="112"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="111"/>
       <c r="K4" s="42">
         <v>0.5</v>
       </c>
-      <c r="L4" s="109"/>
+      <c r="L4" s="122"/>
       <c r="M4" s="16"/>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="90" customHeight="1">
-      <c r="A5" s="103">
+      <c r="A5" s="107">
         <v>6487</v>
       </c>
-      <c r="B5" s="118" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="114" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="111">
+      <c r="B5" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="110">
         <v>3092009</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
@@ -2905,33 +2983,33 @@
         <v>2800</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="112" t="s">
-        <v>41</v>
+      <c r="J5" s="111" t="s">
+        <v>43</v>
       </c>
       <c r="K5" s="42">
         <v>0.5</v>
       </c>
-      <c r="L5" s="104" t="s">
-        <v>42</v>
+      <c r="L5" s="117" t="s">
+        <v>44</v>
       </c>
       <c r="M5" s="16"/>
       <c r="O5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="45" customHeight="1">
-      <c r="A6" s="103"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="111"/>
+      <c r="A6" s="107"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
       <c r="E6" s="52" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -2940,27 +3018,27 @@
         <v>531628</v>
       </c>
       <c r="I6" s="6"/>
-      <c r="J6" s="112"/>
+      <c r="J6" s="111"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="105"/>
+      <c r="L6" s="118"/>
       <c r="M6" s="16"/>
       <c r="O6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:24" s="48" customFormat="1" ht="90" customHeight="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="111"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="110"/>
       <c r="E7" s="52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
@@ -2969,37 +3047,37 @@
       <c r="I7" s="57">
         <v>106787</v>
       </c>
-      <c r="J7" s="112"/>
+      <c r="J7" s="111"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="106"/>
+      <c r="L7" s="119"/>
       <c r="M7" s="50"/>
       <c r="N7"/>
       <c r="O7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7"/>
     </row>
-    <row r="8" spans="1:24" ht="45.75">
-      <c r="A8" s="110" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="112" t="s">
-        <v>52</v>
+    <row r="8" spans="1:24" ht="45">
+      <c r="A8" s="116" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="111" t="s">
+        <v>54</v>
       </c>
       <c r="C8" s="113"/>
-      <c r="D8" s="111">
+      <c r="D8" s="110">
         <v>4250000</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
@@ -3008,33 +3086,33 @@
         <v>400</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="J8" s="109" t="s">
+        <v>58</v>
       </c>
       <c r="K8" s="42">
         <v>0.3</v>
       </c>
-      <c r="L8" s="107"/>
+      <c r="L8" s="120"/>
       <c r="M8" s="16"/>
       <c r="O8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="30.75">
-      <c r="A9" s="110"/>
-      <c r="B9" s="112"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="30">
+      <c r="A9" s="116"/>
+      <c r="B9" s="111"/>
       <c r="C9" s="113"/>
-      <c r="D9" s="111"/>
+      <c r="D9" s="110"/>
       <c r="E9" s="52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -3043,48 +3121,48 @@
         <v>4</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="114"/>
+      <c r="J9" s="109"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="108"/>
+      <c r="L9" s="121"/>
       <c r="M9" s="16"/>
       <c r="O9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="30.75">
-      <c r="A10" s="110"/>
-      <c r="B10" s="112"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="30">
+      <c r="A10" s="116"/>
+      <c r="B10" s="111"/>
       <c r="C10" s="113"/>
-      <c r="D10" s="111"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="114"/>
+      <c r="J10" s="109"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="108"/>
+      <c r="L10" s="121"/>
       <c r="M10" s="16"/>
     </row>
-    <row r="11" spans="1:24" ht="60.75">
-      <c r="A11" s="103"/>
-      <c r="B11" s="112"/>
+    <row r="11" spans="1:24" ht="60">
+      <c r="A11" s="107"/>
+      <c r="B11" s="111"/>
       <c r="C11" s="113"/>
-      <c r="D11" s="111"/>
+      <c r="D11" s="110"/>
       <c r="E11" s="52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -3093,27 +3171,27 @@
         <v>10</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="114"/>
+      <c r="J11" s="109"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="108"/>
+      <c r="L11" s="121"/>
       <c r="M11" s="16"/>
       <c r="O11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="75" customHeight="1">
-      <c r="A12" s="103"/>
-      <c r="B12" s="112"/>
+      <c r="A12" s="107"/>
+      <c r="B12" s="111"/>
       <c r="C12" s="113"/>
-      <c r="D12" s="111"/>
+      <c r="D12" s="110"/>
       <c r="E12" s="52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
@@ -3122,58 +3200,58 @@
         <v>55000</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="114"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="42">
         <v>0.3</v>
       </c>
-      <c r="L12" s="108"/>
+      <c r="L12" s="121"/>
       <c r="M12" s="16"/>
       <c r="O12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="91.5">
-      <c r="A13" s="103"/>
-      <c r="B13" s="112"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="90">
+      <c r="A13" s="107"/>
+      <c r="B13" s="111"/>
       <c r="C13" s="113"/>
-      <c r="D13" s="111"/>
+      <c r="D13" s="110"/>
       <c r="E13" s="52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="6">
         <v>5</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="114"/>
+      <c r="J13" s="109"/>
       <c r="K13" s="42">
         <v>0.3</v>
       </c>
-      <c r="L13" s="108"/>
+      <c r="L13" s="121"/>
       <c r="M13" s="16"/>
       <c r="O13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="90" customHeight="1">
-      <c r="A14" s="103"/>
-      <c r="B14" s="112"/>
+      <c r="A14" s="107"/>
+      <c r="B14" s="111"/>
       <c r="C14" s="113"/>
-      <c r="D14" s="111"/>
+      <c r="D14" s="110"/>
       <c r="E14" s="52" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
@@ -3182,35 +3260,35 @@
         <v>120</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="114"/>
+      <c r="J14" s="109"/>
       <c r="K14" s="42">
         <v>0.1</v>
       </c>
-      <c r="L14" s="109"/>
+      <c r="L14" s="122"/>
       <c r="M14" s="16"/>
       <c r="O14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="60.75">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="75">
       <c r="A15" s="36">
         <v>125754</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="23">
         <v>55000</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
@@ -3219,41 +3297,41 @@
         <v>200</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K15" s="42">
         <v>0.5</v>
       </c>
       <c r="L15" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M15" s="16"/>
       <c r="O15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="30" customHeight="1">
-      <c r="A16" s="110" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="103" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="111">
+      <c r="A16" s="116" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="107"/>
+      <c r="D16" s="110">
         <v>11182694</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -3261,32 +3339,32 @@
       <c r="H16" s="33">
         <v>4449727</v>
       </c>
-      <c r="I16" s="103" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="103" t="s">
-        <v>56</v>
+      <c r="I16" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="107" t="s">
+        <v>58</v>
       </c>
       <c r="K16" s="4"/>
-      <c r="L16" s="107"/>
+      <c r="L16" s="120"/>
       <c r="M16" s="16"/>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="30.75">
-      <c r="A17" s="110"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="111"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="30">
+      <c r="A17" s="116"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="53" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
@@ -3294,55 +3372,55 @@
       <c r="H17" s="33">
         <v>8</v>
       </c>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="108"/>
+      <c r="L17" s="121"/>
       <c r="M17" s="16"/>
       <c r="O17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="30.75">
-      <c r="A18" s="110"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="111"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="30">
+      <c r="A18" s="116"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="110"/>
       <c r="E18" s="53" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" s="41">
         <v>0</v>
       </c>
       <c r="H18" s="40"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="108"/>
+      <c r="L18" s="121"/>
       <c r="M18" s="16"/>
       <c r="O18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A19" s="110"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="111"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A19" s="116"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="110"/>
       <c r="E19" s="54" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="47">
         <v>0</v>
@@ -3350,31 +3428,31 @@
       <c r="H19" s="45">
         <v>65</v>
       </c>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
       <c r="K19" s="47"/>
-      <c r="L19" s="108"/>
+      <c r="L19" s="121"/>
       <c r="M19" s="49"/>
       <c r="O19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q19"/>
       <c r="R19"/>
       <c r="S19"/>
     </row>
-    <row r="20" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A20" s="110"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="111"/>
+    <row r="20" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A20" s="116"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="110"/>
       <c r="E20" s="54" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="47">
         <v>0</v>
@@ -3382,31 +3460,31 @@
       <c r="H20" s="45">
         <v>42</v>
       </c>
-      <c r="I20" s="103"/>
-      <c r="J20" s="103"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
       <c r="K20" s="47"/>
-      <c r="L20" s="108"/>
+      <c r="L20" s="121"/>
       <c r="M20" s="49"/>
       <c r="O20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q20"/>
       <c r="R20"/>
       <c r="S20"/>
     </row>
-    <row r="21" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A21" s="110"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="111"/>
+    <row r="21" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A21" s="116"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="110"/>
       <c r="E21" s="54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G21" s="47">
         <v>0</v>
@@ -3414,31 +3492,31 @@
       <c r="H21" s="45">
         <v>17</v>
       </c>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
       <c r="K21" s="47"/>
-      <c r="L21" s="108"/>
+      <c r="L21" s="121"/>
       <c r="M21" s="49"/>
       <c r="O21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q21"/>
       <c r="R21"/>
       <c r="S21"/>
     </row>
-    <row r="22" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A22" s="110"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="111"/>
+    <row r="22" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A22" s="116"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="110"/>
       <c r="E22" s="54" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" s="47">
         <v>0</v>
@@ -3446,31 +3524,31 @@
       <c r="H22" s="45">
         <v>113</v>
       </c>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
       <c r="K22" s="47"/>
-      <c r="L22" s="108"/>
+      <c r="L22" s="121"/>
       <c r="M22" s="49"/>
       <c r="O22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q22"/>
       <c r="R22"/>
       <c r="S22"/>
     </row>
-    <row r="23" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A23" s="110"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="111"/>
+    <row r="23" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A23" s="116"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="110"/>
       <c r="E23" s="54" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G23" s="47">
         <v>0</v>
@@ -3478,37 +3556,37 @@
       <c r="H23" s="45">
         <v>3001</v>
       </c>
-      <c r="I23" s="103"/>
-      <c r="J23" s="103"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
       <c r="K23" s="47"/>
-      <c r="L23" s="109"/>
+      <c r="L23" s="122"/>
       <c r="M23" s="49"/>
       <c r="O23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
     </row>
-    <row r="24" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A24" s="110" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="103"/>
-      <c r="D24" s="111">
+    <row r="24" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A24" s="116" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="107" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="107"/>
+      <c r="D24" s="110">
         <v>6148000</v>
       </c>
       <c r="E24" s="54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G24" s="47">
         <v>0</v>
@@ -3517,34 +3595,34 @@
         <v>100</v>
       </c>
       <c r="I24" s="47"/>
-      <c r="J24" s="103" t="s">
-        <v>84</v>
+      <c r="J24" s="107" t="s">
+        <v>86</v>
       </c>
       <c r="K24" s="47"/>
-      <c r="L24" s="104" t="s">
-        <v>27</v>
+      <c r="L24" s="117" t="s">
+        <v>28</v>
       </c>
       <c r="M24" s="49"/>
       <c r="O24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24"/>
     </row>
-    <row r="25" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A25" s="110"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="111"/>
+    <row r="25" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A25" s="116"/>
+      <c r="B25" s="107"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="54" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" s="47">
         <v>0</v>
@@ -3553,30 +3631,30 @@
         <v>1000</v>
       </c>
       <c r="I25" s="47"/>
-      <c r="J25" s="103"/>
+      <c r="J25" s="107"/>
       <c r="K25" s="47"/>
-      <c r="L25" s="105"/>
+      <c r="L25" s="118"/>
       <c r="M25" s="49"/>
       <c r="O25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25"/>
     </row>
-    <row r="26" spans="1:19" ht="30.75">
-      <c r="A26" s="110"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="111"/>
+    <row r="26" spans="1:19" ht="30">
+      <c r="A26" s="116"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="53" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
@@ -3585,25 +3663,25 @@
         <v>2</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="103"/>
+      <c r="J26" s="107"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="105"/>
+      <c r="L26" s="118"/>
       <c r="M26" s="50"/>
       <c r="O26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="110"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="111"/>
+      <c r="A27" s="116"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="110"/>
       <c r="E27" s="53"/>
       <c r="F27" s="38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
@@ -3612,27 +3690,27 @@
         <v>0.4</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="103"/>
+      <c r="J27" s="107"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="105"/>
+      <c r="L27" s="118"/>
       <c r="M27" s="50"/>
       <c r="O27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="48" customFormat="1" ht="30.75">
-      <c r="A28" s="110"/>
-      <c r="B28" s="103"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="111"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="48" customFormat="1" ht="30">
+      <c r="A28" s="116"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="110"/>
       <c r="E28" s="54" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G28" s="47">
         <v>0</v>
@@ -3641,15 +3719,15 @@
         <v>10000</v>
       </c>
       <c r="I28" s="47"/>
-      <c r="J28" s="103"/>
+      <c r="J28" s="107"/>
       <c r="K28" s="47"/>
-      <c r="L28" s="106"/>
+      <c r="L28" s="119"/>
       <c r="M28" s="49"/>
       <c r="O28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q28"/>
       <c r="R28"/>
@@ -3660,38 +3738,38 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J16:J23"/>
+    <mergeCell ref="L24:L28"/>
+    <mergeCell ref="L16:L23"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="L8:L14"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="B8:B14"/>
+    <mergeCell ref="C8:C14"/>
+    <mergeCell ref="D8:D14"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="I16:I23"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="C16:C23"/>
-    <mergeCell ref="D16:D23"/>
-    <mergeCell ref="I16:I23"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="B8:B14"/>
-    <mergeCell ref="C8:C14"/>
-    <mergeCell ref="D8:D14"/>
-    <mergeCell ref="J8:J14"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="J16:J23"/>
-    <mergeCell ref="L24:L28"/>
-    <mergeCell ref="L16:L23"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="L8:L14"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="J5:J7"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{4508A1F8-96DE-41B3-8189-7C0C3128B039}"/>
@@ -3771,195 +3849,195 @@
         <v>122659</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="23">
         <v>149000</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="60">
-      <c r="A3" s="122">
+      <c r="A3" s="130">
         <v>122627</v>
       </c>
-      <c r="B3" s="114" t="s">
-        <v>29</v>
+      <c r="B3" s="109" t="s">
+        <v>31</v>
       </c>
       <c r="C3" s="113"/>
-      <c r="D3" s="126">
+      <c r="D3" s="134">
         <v>922000</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="136" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="121.5">
-      <c r="A4" s="123"/>
-      <c r="B4" s="114"/>
+        <v>34</v>
+      </c>
+      <c r="J3" s="144" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="135">
+      <c r="A4" s="131"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="113"/>
-      <c r="D4" s="128"/>
+      <c r="D4" s="136"/>
       <c r="E4" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="136"/>
+        <v>102</v>
+      </c>
+      <c r="J4" s="144"/>
     </row>
     <row r="5" spans="1:14" ht="90" customHeight="1">
-      <c r="A5" s="104">
+      <c r="A5" s="117">
         <v>6487</v>
       </c>
-      <c r="B5" s="130" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="133" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="126">
+      <c r="B5" s="138" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="141" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="134">
         <v>3092009</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I5" s="12"/>
-      <c r="J5" s="137" t="s">
-        <v>41</v>
+      <c r="J5" s="145" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="45" customHeight="1">
-      <c r="A6" s="105"/>
-      <c r="B6" s="131"/>
-      <c r="C6" s="134"/>
-      <c r="D6" s="127"/>
+      <c r="A6" s="118"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="135"/>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="137"/>
+        <v>106</v>
+      </c>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:14" ht="90" customHeight="1">
-      <c r="A7" s="106"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="128"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="136"/>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="137"/>
-    </row>
-    <row r="8" spans="1:14" ht="45.75">
-      <c r="A8" s="124" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="126">
+        <v>108</v>
+      </c>
+      <c r="J7" s="145"/>
+    </row>
+    <row r="8" spans="1:14" ht="45">
+      <c r="A8" s="132" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="120"/>
+      <c r="D8" s="134">
         <v>4250000</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="138" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="30.75">
-      <c r="A9" s="125"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="127"/>
+        <v>57</v>
+      </c>
+      <c r="J8" s="126" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="30">
+      <c r="A9" s="133"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="135"/>
       <c r="E9" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -3968,18 +4046,18 @@
         <v>4</v>
       </c>
       <c r="I9" s="8"/>
-      <c r="J9" s="138"/>
-    </row>
-    <row r="10" spans="1:14" ht="30.75">
-      <c r="A10" s="125"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="127"/>
+      <c r="J9" s="126"/>
+    </row>
+    <row r="10" spans="1:14" ht="30">
+      <c r="A10" s="133"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="135"/>
       <c r="E10" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -3989,18 +4067,18 @@
         <v>6400</v>
       </c>
       <c r="I10" s="8"/>
-      <c r="J10" s="138"/>
+      <c r="J10" s="126"/>
     </row>
     <row r="11" spans="1:14" ht="60">
-      <c r="A11" s="105"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="127"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -4009,9 +4087,9 @@
         <v>10</v>
       </c>
       <c r="I11" s="8"/>
-      <c r="J11" s="138"/>
+      <c r="J11" s="126"/>
       <c r="L11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M11">
         <f>SUM(H9+H17+H26)</f>
@@ -4023,26 +4101,26 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="75">
-      <c r="A12" s="105"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="127"/>
+      <c r="A12" s="118"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="135"/>
       <c r="E12" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I12" s="15"/>
-      <c r="J12" s="138"/>
+      <c r="J12" s="126"/>
       <c r="L12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M12">
         <f>SUM(H10+H18+H27)</f>
@@ -4050,89 +4128,89 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="75">
-      <c r="A13" s="105"/>
-      <c r="B13" s="112"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="127"/>
+      <c r="A13" s="118"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="135"/>
       <c r="E13" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I13" s="16"/>
-      <c r="J13" s="138"/>
+      <c r="J13" s="126"/>
     </row>
     <row r="14" spans="1:14" ht="90">
-      <c r="A14" s="105"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="128"/>
+      <c r="A14" s="118"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="136"/>
       <c r="E14" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="10">
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I14" s="17"/>
-      <c r="J14" s="138"/>
-    </row>
-    <row r="15" spans="1:14" ht="60">
+      <c r="J14" s="126"/>
+    </row>
+    <row r="15" spans="1:14" ht="75">
       <c r="A15" s="26">
         <v>125754</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="24">
         <v>55000</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15" s="10">
         <v>0</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="30">
-      <c r="A16" s="141" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="139"/>
-      <c r="D16" s="140">
+      <c r="A16" s="123" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="125"/>
+      <c r="D16" s="124">
         <v>11182694</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="20">
         <v>0</v>
@@ -4140,23 +4218,23 @@
       <c r="H16" s="21">
         <v>4449727</v>
       </c>
-      <c r="I16" s="119" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="119" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30.75">
-      <c r="A17" s="141"/>
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="140"/>
+      <c r="I16" s="127" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="127" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30">
+      <c r="A17" s="123"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="124"/>
       <c r="E17" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G17" s="20">
         <v>0</v>
@@ -4164,19 +4242,19 @@
       <c r="H17" s="21">
         <v>8</v>
       </c>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="30.75">
-      <c r="A18" s="141"/>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="140"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+    </row>
+    <row r="18" spans="1:10" ht="30">
+      <c r="A18" s="123"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="124"/>
       <c r="E18" s="29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" s="31">
         <v>0</v>
@@ -4185,19 +4263,19 @@
         <f>H17*1600</f>
         <v>12800</v>
       </c>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="30.75">
-      <c r="A19" s="141"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="140"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+    </row>
+    <row r="19" spans="1:10" ht="30">
+      <c r="A19" s="123"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="124"/>
       <c r="E19" s="21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="20">
         <v>0</v>
@@ -4205,19 +4283,19 @@
       <c r="H19" s="21">
         <v>65</v>
       </c>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
     </row>
     <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="141"/>
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="140"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="124"/>
       <c r="E20" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="20">
         <v>0</v>
@@ -4225,19 +4303,19 @@
       <c r="H20" s="21">
         <v>42</v>
       </c>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
     </row>
     <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="141"/>
-      <c r="B21" s="139"/>
-      <c r="C21" s="139"/>
-      <c r="D21" s="140"/>
+      <c r="A21" s="123"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="124"/>
       <c r="E21" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G21" s="20">
         <v>0</v>
@@ -4245,19 +4323,19 @@
       <c r="H21" s="21">
         <v>17</v>
       </c>
-      <c r="I21" s="120"/>
-      <c r="J21" s="120"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
     </row>
     <row r="22" spans="1:10" ht="30">
-      <c r="A22" s="141"/>
-      <c r="B22" s="139"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="140"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="124"/>
       <c r="E22" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" s="20">
         <v>0</v>
@@ -4265,19 +4343,19 @@
       <c r="H22" s="21">
         <v>113</v>
       </c>
-      <c r="I22" s="120"/>
-      <c r="J22" s="120"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
     </row>
     <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="141"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="140"/>
+      <c r="A23" s="123"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="124"/>
       <c r="E23" s="21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G23" s="20">
         <v>0</v>
@@ -4285,25 +4363,25 @@
       <c r="H23" s="21">
         <v>3001</v>
       </c>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="141" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="139" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="140">
+      <c r="A24" s="123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="125" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="125"/>
+      <c r="D24" s="124">
         <v>6148000</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G24" s="20">
         <v>0</v>
@@ -4312,20 +4390,20 @@
         <v>100</v>
       </c>
       <c r="I24" s="20"/>
-      <c r="J24" s="119" t="s">
-        <v>84</v>
+      <c r="J24" s="127" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="141"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="140"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="124"/>
       <c r="E25" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" s="20">
         <v>0</v>
@@ -4334,18 +4412,18 @@
         <v>2</v>
       </c>
       <c r="I25" s="20"/>
-      <c r="J25" s="120"/>
+      <c r="J25" s="128"/>
     </row>
     <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="141"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="140"/>
+      <c r="A26" s="123"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="124"/>
       <c r="E26" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G26" s="20">
         <v>0</v>
@@ -4354,18 +4432,18 @@
         <v>2</v>
       </c>
       <c r="I26" s="20"/>
-      <c r="J26" s="120"/>
-    </row>
-    <row r="27" spans="1:10" ht="30.75">
-      <c r="A27" s="141"/>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="140"/>
+      <c r="J26" s="128"/>
+    </row>
+    <row r="27" spans="1:10" ht="30">
+      <c r="A27" s="123"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="124"/>
       <c r="E27" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G27" s="20">
         <v>0</v>
@@ -4375,18 +4453,18 @@
         <v>3200</v>
       </c>
       <c r="I27" s="20"/>
-      <c r="J27" s="120"/>
+      <c r="J27" s="128"/>
     </row>
     <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="141"/>
-      <c r="B28" s="139"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="140"/>
+      <c r="A28" s="123"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="124"/>
       <c r="E28" s="21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G28" s="20">
         <v>0</v>
@@ -4395,7 +4473,7 @@
         <v>10000</v>
       </c>
       <c r="I28" s="20"/>
-      <c r="J28" s="121"/>
+      <c r="J28" s="129"/>
     </row>
     <row r="30" spans="1:10">
       <c r="B30" s="28"/>
@@ -4408,16 +4486,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="J8:J14"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="C16:C23"/>
-    <mergeCell ref="D16:D23"/>
-    <mergeCell ref="J16:J23"/>
     <mergeCell ref="J24:J28"/>
     <mergeCell ref="I16:I23"/>
     <mergeCell ref="A3:A4"/>
@@ -4434,6 +4502,16 @@
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="J16:J23"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4470,172 +4548,172 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="142" t="s">
-        <v>30</v>
+    <row r="2" spans="1:2" ht="45">
+      <c r="A2" s="147" t="s">
+        <v>32</v>
       </c>
       <c r="B2" s="95" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="142" t="s">
-        <v>57</v>
+      <c r="A3" s="147" t="s">
+        <v>59</v>
       </c>
       <c r="B3" s="95" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="142" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45">
+      <c r="A4" s="147" t="s">
+        <v>119</v>
       </c>
       <c r="B4" s="95" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="142" t="s">
-        <v>117</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="147" t="s">
+        <v>121</v>
       </c>
       <c r="B5" s="95" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="142" t="s">
-        <v>74</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="90">
+      <c r="A6" s="147" t="s">
+        <v>76</v>
       </c>
       <c r="B6" s="95" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="142" t="s">
-        <v>76</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="147" t="s">
+        <v>78</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="142" t="s">
-        <v>23</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="147" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="95" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="142" t="s">
-        <v>79</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="147" t="s">
+        <v>81</v>
       </c>
       <c r="B9" s="95" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="142" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="143" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="142" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="143" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="142" t="s">
-        <v>86</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="148" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="147" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="148" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" s="147" t="s">
+        <v>88</v>
       </c>
       <c r="B12" s="95" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="142" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="143" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="148" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="142" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="143" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="142" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="143" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="142" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="143" t="s">
+      <c r="A14" s="147" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="142" t="s">
-        <v>64</v>
+      <c r="B14" s="148" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" s="147" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="148" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30">
+      <c r="A16" s="147" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="148" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="147" t="s">
+        <v>66</v>
       </c>
       <c r="B17" s="95" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="142" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="143" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="142" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="143" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="142" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="143" t="s">
+    <row r="18" spans="1:2" ht="30">
+      <c r="A18" s="147" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="142" t="s">
+      <c r="B18" s="148" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="75">
+      <c r="A19" s="147" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="148" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30">
+      <c r="A20" s="147" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="148" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45">
+      <c r="A21" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="144" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="142" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="143" t="s">
-        <v>140</v>
+      <c r="B21" s="149" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="147" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="148" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4644,15 +4722,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -4675,9 +4744,18 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -4702,6 +4780,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4781,6 +4860,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4925,13 +5009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D725300-A553-47A2-B3D8-21DC5742429F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B2F36C-ED54-4CE9-938D-170704522F69}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D725300-A553-47A2-B3D8-21DC5742429F}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749CB1BA-1022-4E25-B9B0-E9E22067111A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53A75986-DE0B-4FB6-8F95-218A73D50C7D}"/>
 </file>
--- a/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iraq - Energy Projects.xlsx
@@ -655,10 +655,10 @@
     <xf numFmtId="165" fontId="10" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -755,6 +755,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1328,15 +1348,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="126" t="n"/>
-      <c r="M3" s="127" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K3" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="127" t="n"/>
+      <c r="M3" s="107" t="n"/>
       <c r="N3" s="107" t="n"/>
       <c r="O3" s="111" t="n"/>
       <c r="P3" s="112" t="n"/>
@@ -2065,14 +2081,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="2">
     <dataValidation sqref="E1 E9:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1"/>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
@@ -2084,6 +2094,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3784,9 +3795,8 @@
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6">
-        <f>1600*H9</f>
-        <v/>
+      <c r="H10" s="6" t="n">
+        <v>6400</v>
       </c>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="134" t="n"/>
@@ -3819,13 +3829,11 @@
           <t>total MW</t>
         </is>
       </c>
-      <c r="M11">
-        <f>SUM(H9+H17+H26)</f>
-        <v/>
-      </c>
-      <c r="N11">
-        <f>M11*1600</f>
-        <v/>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22400</v>
       </c>
     </row>
     <row r="12" ht="75" customHeight="1">
@@ -3858,9 +3866,8 @@
           <t>total MWh</t>
         </is>
       </c>
-      <c r="M12">
-        <f>SUM(H10+H18+H27)</f>
-        <v/>
+      <c r="M12" t="n">
+        <v>22400</v>
       </c>
     </row>
     <row r="13" ht="75" customHeight="1">
@@ -4039,9 +4046,8 @@
       <c r="G18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="29">
-        <f>H17*1600</f>
-        <v/>
+      <c r="H18" s="29" t="n">
+        <v>12800</v>
       </c>
       <c r="I18" s="134" t="n"/>
       <c r="J18" s="134" t="n"/>
@@ -4270,9 +4276,8 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="95">
-        <f>H26*1600</f>
-        <v/>
+      <c r="H27" s="95" t="n">
+        <v>3200</v>
       </c>
       <c r="I27" s="20" t="n"/>
       <c r="J27" s="134" t="n"/>
@@ -4305,9 +4310,8 @@
       <c r="B30" s="28" t="n"/>
     </row>
     <row r="31">
-      <c r="H31">
-        <f>H27+H18+H10</f>
-        <v/>
+      <c r="H31" t="n">
+        <v>22400</v>
       </c>
     </row>
   </sheetData>
